--- a/Result/profitability/8016.xlsx
+++ b/Result/profitability/8016.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>3.49625</v>
+        <v>3.9725</v>
       </c>
       <c r="N2" t="n">
-        <v>30.4425</v>
+        <v>30.6625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15375</v>
+        <v>3.67625</v>
       </c>
       <c r="N3" t="n">
-        <v>28.9675</v>
+        <v>29.21625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>2.94375</v>
+        <v>3.4725</v>
       </c>
       <c r="N4" t="n">
-        <v>27.80375</v>
+        <v>28.0775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5175</v>
+        <v>3.0325</v>
       </c>
       <c r="N5" t="n">
-        <v>26.60625</v>
+        <v>27.13</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.48</v>
       </c>
       <c r="M6" t="n">
-        <v>2.1325</v>
+        <v>2.6825</v>
       </c>
       <c r="N6" t="n">
-        <v>25.33375</v>
+        <v>26.075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.85375</v>
+        <v>2.27</v>
       </c>
       <c r="N7" t="n">
-        <v>24.89875</v>
+        <v>25.44625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.47875</v>
+        <v>1.86375</v>
       </c>
       <c r="N8" t="n">
-        <v>24.295</v>
+        <v>24.73375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6252</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4074</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2178</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1028</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>189</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1216</v>
+      </c>
+      <c r="K75" t="n">
+        <v>904</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.28625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.84625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6695652173913045</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.510000000000005</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1120331950207472</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4.119999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.157303370786517</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.190000000000005</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.136704730831974</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
